--- a/Result/profitability/6129.xlsx
+++ b/Result/profitability/6129.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,25 +669,25 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.245</v>
+        <v>-0.1975</v>
       </c>
       <c r="N2" t="n">
-        <v>31.4</v>
+        <v>32.09</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.20875</v>
+        <v>-0.19125</v>
       </c>
       <c r="N3" t="n">
-        <v>31.34125</v>
+        <v>31.7625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.18125</v>
+        <v>-0.12625</v>
       </c>
       <c r="N4" t="n">
-        <v>30.93875</v>
+        <v>31.255</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.095</v>
+        <v>-0.06249999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>31.24875</v>
+        <v>31.18125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07625</v>
+        <v>-0.05375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>31.03375</v>
+        <v>31.1775</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06375</v>
+        <v>-0.0525</v>
       </c>
       <c r="N7" t="n">
-        <v>31.16625</v>
+        <v>31.6425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006249999999999999</v>
+        <v>0.02375</v>
       </c>
       <c r="N8" t="n">
-        <v>31.85375</v>
+        <v>31.91125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07750000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="N9" t="n">
         <v>32.40125</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>390</v>
+      </c>
+      <c r="D75" t="n">
+        <v>257</v>
+      </c>
+      <c r="E75" t="n">
+        <v>133</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-8.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.23375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.1325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8235294117647058</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4600000000000009</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01364580243251257</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.896551724137931</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5399999999999991</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0155574762316335</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
